--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260702_205302.xlsx
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
